--- a/AAII_Financials/Quarterly/BSAC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BSAC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>BSAC</t>
   </si>
@@ -656,350 +656,357 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AQ102"/>
+  <dimension ref="A5:AR102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AQ7" s="2">
+      <c r="AR7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>768400</v>
+      </c>
+      <c r="E8" s="3">
         <v>618000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>599000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>590800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>632200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>619700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>606400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>624000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>560500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>422900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>496400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>342100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>450000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>473300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1196500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1219000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1176300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>848300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>876900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>704000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>666700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>588100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>722100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>504000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>635800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>762100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>795900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>758500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>933000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>599000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>746000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>704500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>717700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>675900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>770700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>675200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>809800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>770200</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>794800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>809000</v>
       </c>
-      <c r="AQ8" s="3">
+      <c r="AR8" s="3">
         <v>839900</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E9" s="3">
         <v>8200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>7800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>7500</v>
-      </c>
-      <c r="K9" s="3">
-        <v>6700</v>
       </c>
       <c r="L9" s="3">
         <v>6700</v>
       </c>
       <c r="M9" s="3">
+        <v>6700</v>
+      </c>
+      <c r="N9" s="3">
         <v>7800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8300</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1078,53 +1085,56 @@
       <c r="AQ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AR9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>763500</v>
+      </c>
+      <c r="E10" s="3">
         <v>609900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>593100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>585300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>624400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>613300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>599600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>616500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>553700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>416100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>488600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>336200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>443700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>465000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1203,8 +1213,11 @@
       <c r="AQ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AR10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1248,8 +1261,9 @@
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
       <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1373,8 +1387,11 @@
       <c r="AQ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AR12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1498,53 +1515,56 @@
       <c r="AQ13" s="3">
         <v>0</v>
       </c>
+      <c r="AR13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E14" s="3">
         <v>10100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>17700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>16800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>21500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>16300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1623,133 +1643,139 @@
       <c r="AQ14" s="3">
         <v>0</v>
       </c>
+      <c r="AR14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E15" s="3">
         <v>13500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>28500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>13400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>14500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>13600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>13300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>14300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-36500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-35000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-34400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-35700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-47300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-52100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-48800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-37800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-30800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-30900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-34200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-33000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-35100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-36400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-35200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-34000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-27400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-23900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-24700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-24600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-32900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-28000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-27600</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-25900</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-28400</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-24700</v>
       </c>
-      <c r="AQ15" s="3">
+      <c r="AR15" s="3">
         <v>-23900</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1790,258 +1816,265 @@
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
       <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
     </row>
-    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>271900</v>
+      </c>
+      <c r="E17" s="3">
         <v>246100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>270800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>257400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>274900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>268000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>248100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>270900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>260600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>247400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>257500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>258100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>275900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>273900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1018900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>885100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>708700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>442700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>360600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>215400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>208300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>184400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>320300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>214800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>401100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>422500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>511700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>442800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>527300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>278600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>384900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>381700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>367900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>328600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>374300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>314200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>416500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>410500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>449100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>462900</v>
       </c>
-      <c r="AQ17" s="3">
+      <c r="AR17" s="3">
         <v>469900</v>
       </c>
     </row>
-    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>496500</v>
+      </c>
+      <c r="E18" s="3">
         <v>371900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>328300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>333400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>357400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>351700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>358300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>353100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>299800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>175500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>238900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>84000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>174100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>199500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>177600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>333800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>467600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>405600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>516300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>488600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>458300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>403700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>401800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>289200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>234700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>339700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>284200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>315700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>405800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>320400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>361100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>322800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>349900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>347300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>396500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>361000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>393300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>359700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>345700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>346100</v>
       </c>
-      <c r="AQ18" s="3">
+      <c r="AR18" s="3">
         <v>370000</v>
       </c>
     </row>
-    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2085,8 +2118,9 @@
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
       <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
     </row>
-    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2129,214 +2163,220 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-72300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-115400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-123600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-77000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-191200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-199100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-151500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-141700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-152200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-127900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-91700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-129800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-92800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-75100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-119900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-102200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-105500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-112800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-100000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-96000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-148900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-81100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-125900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-94800</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-139800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-116700</v>
       </c>
-      <c r="AQ20" s="3">
+      <c r="AR20" s="3">
         <v>-161800</v>
       </c>
     </row>
-    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>508100</v>
+      </c>
+      <c r="E21" s="3">
         <v>385400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>356700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>346100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>369300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>364800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>383300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>366500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>312400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>187600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>253400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>97600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>187400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>213800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>141900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>253400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>378400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>364300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>362100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>330000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>345400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>293000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>280400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>192300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>177200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>242900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>226600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>277000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>321100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>252200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>283000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>233900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>274500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>275900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>280400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>307900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>294900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>290800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>234300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>254100</v>
       </c>
-      <c r="AQ21" s="3">
+      <c r="AR21" s="3">
         <v>232100</v>
       </c>
     </row>
-    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2379,8 +2419,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2460,258 +2500,267 @@
       <c r="AQ22" s="3">
         <v>0</v>
       </c>
+      <c r="AR22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>489500</v>
+      </c>
+      <c r="E23" s="3">
         <v>361800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>310600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>316600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>350700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>351500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>336800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>341500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>296900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>161800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>222600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>83900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>173800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>199000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>105400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>218400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>344000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>328600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>325100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>289500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>306900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>262000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>249600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>161300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>143100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>209900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>191500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>240600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>285900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>218100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>255600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>210000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>249800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>251300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>247600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>279900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>267300</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>264900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>205900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>229400</v>
       </c>
-      <c r="AQ23" s="3">
+      <c r="AR23" s="3">
         <v>208200</v>
       </c>
     </row>
-    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E24" s="3">
         <v>60100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>56800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>55800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>53500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>55500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>66000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>66100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>62900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>36200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>21100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>8300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>22500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>11500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>37100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>57800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>49800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>63000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>68000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>55600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>41500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>38000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>36900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>37500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>41800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>51400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>51500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>54800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>53500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>48600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>51200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>57000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>55800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>54800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>45800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>54700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>41000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>44100</v>
       </c>
-      <c r="AQ24" s="3">
+      <c r="AR24" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2835,258 +2884,267 @@
       <c r="AQ25" s="3">
         <v>0</v>
       </c>
+      <c r="AR25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>425300</v>
+      </c>
+      <c r="E26" s="3">
         <v>301700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>253800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>260900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>297200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>296000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>270700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>275400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>234100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>125600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>201400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>69000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>165500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>176500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>113200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>207000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>306900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>270900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>275300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>226400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>238900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>206400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>208100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>123400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>106100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>172300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>149700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>189100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>234400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>163400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>202100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>161400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>198600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>194300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>191700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>225100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>221500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>210200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>164900</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>185200</v>
       </c>
-      <c r="AQ26" s="3">
+      <c r="AR26" s="3">
         <v>176300</v>
       </c>
     </row>
-    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>415300</v>
+      </c>
+      <c r="E27" s="3">
         <v>293800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>248400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>257400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>292600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>291900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>273600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>270900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>231000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>122700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>201800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>63400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>158500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>171300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>109900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>202300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>302600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>266400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>271900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>222400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>236900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>203900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>205400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>122000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>105200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>171400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>148200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>188700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>234000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>163100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>198900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>160900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>197800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>193300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>198000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>201900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>221100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>209300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>164000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>184200</v>
       </c>
-      <c r="AQ27" s="3">
+      <c r="AR27" s="3">
         <v>175600</v>
       </c>
     </row>
-    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3210,8 +3268,11 @@
       <c r="AQ28" s="3">
         <v>0</v>
       </c>
+      <c r="AR28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3275,8 +3336,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -3290,18 +3351,18 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>2300</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3314,8 +3375,8 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL29" s="3">
         <v>0</v>
@@ -3335,8 +3396,11 @@
       <c r="AQ29" s="3">
         <v>0</v>
       </c>
+      <c r="AR29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3460,8 +3524,11 @@
       <c r="AQ30" s="3">
         <v>0</v>
       </c>
+      <c r="AR30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3585,8 +3652,11 @@
       <c r="AQ31" s="3">
         <v>0</v>
       </c>
+      <c r="AR31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3629,214 +3699,220 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>72300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>115400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>123600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>77000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>191200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>199100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>151500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>141700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>152200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>127900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>91700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>129800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>92800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>75100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>119900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>102200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>105500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>112800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>100000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>96000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>148900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>81100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>125900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>94800</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>139800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>116700</v>
       </c>
-      <c r="AQ32" s="3">
+      <c r="AR32" s="3">
         <v>161800</v>
       </c>
     </row>
-    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>415300</v>
+      </c>
+      <c r="E33" s="3">
         <v>293800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>248400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>257400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>292600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>291900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>273600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>270900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>231000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>122700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>201800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>63400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>158500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>171300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>109900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>202300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>302600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>266400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>271900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>222400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>236900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>203900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>205400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>122000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>105200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>171400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>148200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>188700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>236300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>163100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>198900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>160900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>197800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>193300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>198000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>201900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>221100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>209300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>164000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>184200</v>
       </c>
-      <c r="AQ33" s="3">
+      <c r="AR33" s="3">
         <v>175600</v>
       </c>
     </row>
-    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3960,263 +4036,272 @@
       <c r="AQ34" s="3">
         <v>0</v>
       </c>
+      <c r="AR34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>415300</v>
+      </c>
+      <c r="E35" s="3">
         <v>293800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>248400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>257400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>292600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>291900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>273600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>270900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>231000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>122700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>201800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>63400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>158500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>171300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>109900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>202300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>302600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>266400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>271900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>222400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>236900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>203900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>205400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>122000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>105200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>171400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>148200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>188700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>236300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>163100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>198900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>160900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>197800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>193300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>198000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>201900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>221100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>209300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>164000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>184200</v>
       </c>
-      <c r="AQ35" s="3">
+      <c r="AR35" s="3">
         <v>175600</v>
       </c>
     </row>
-    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AQ38" s="2">
+      <c r="AR38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4260,8 +4345,9 @@
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
+      <c r="AR39" s="3"/>
     </row>
-    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4305,303 +4391,310 @@
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
+      <c r="AR40" s="3"/>
     </row>
-    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3925000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3696200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2883500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3759900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2500000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2840400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2181300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2961300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2662000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2823400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3286100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4972600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3662100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3688600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2626700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2725800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2453500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3094900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2278500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5207000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8679300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1946800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2744800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2768100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3706300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3701400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3761900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2441700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3152000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2445000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2726300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2478200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2247800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2370600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2772100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2610400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2261400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2908200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2786700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2920400</v>
       </c>
-      <c r="AQ41" s="3">
+      <c r="AR41" s="3">
         <v>2699600</v>
       </c>
     </row>
-    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>13425600</v>
+      </c>
+      <c r="E42" s="3">
         <v>13970800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13769700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12552000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12907100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12738600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13878600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13779600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13126100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>14893300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>12528300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>14800100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14047700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>15371300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1318300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2356700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2376500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2202400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>14472500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>14588600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>10106800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>9943900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>11190000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>13925800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>18449000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>19936100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>11914800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>11181500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>6259500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4147600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>4401500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3698900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3812800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3125100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>4590400</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>4490700</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>4978700</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>5720000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>6201200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>5544500</v>
       </c>
-      <c r="AQ42" s="3">
+      <c r="AR42" s="3">
         <v>7224700</v>
       </c>
     </row>
-    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>219400</v>
+      </c>
+      <c r="E43" s="3">
         <v>130700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>106700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>98800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>234500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>226500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>217100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>223400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>277600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>291400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>236800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>299000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>414100</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4680,53 +4773,56 @@
       <c r="AQ43" s="3">
         <v>0</v>
       </c>
+      <c r="AR43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E44" s="3">
         <v>53100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>86400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>53900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>53600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>49200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>64000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>50600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>54500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>46400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>42500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>26800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>39800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>37100</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4805,53 +4901,56 @@
       <c r="AQ44" s="3">
         <v>0</v>
       </c>
+      <c r="AR44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1770600</v>
+      </c>
+      <c r="E45" s="3">
         <v>2714200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2362900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2046700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2063800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2006200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1894100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2022600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2195400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2504800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2575000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2723400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3650900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4078800</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4930,53 +5029,56 @@
       <c r="AQ45" s="3">
         <v>0</v>
       </c>
+      <c r="AR45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>20005800</v>
+      </c>
+      <c r="E46" s="3">
         <v>21015600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19882900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18910900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>17811400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18147000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19436700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19289500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18642300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21188800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19663700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>23048600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22028200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24259000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -5055,383 +5157,395 @@
       <c r="AQ46" s="3">
         <v>0</v>
       </c>
+      <c r="AR46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11254900</v>
+      </c>
+      <c r="E47" s="3">
         <v>9846800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10204900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9399800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9342000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9209100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7974500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>9139000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10852800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12962200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>14564700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13175600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14546600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>14063600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>50300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>46500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>43700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>44000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>44100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>13500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>12400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>12100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>12000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>12600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>13300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>43000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>41000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>40300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>38800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>36200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>40500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>39200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>37000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>36000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>35900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>35300</v>
       </c>
-      <c r="AQ47" s="3">
+      <c r="AR47" s="3">
         <v>33600</v>
       </c>
     </row>
-    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>288200</v>
+      </c>
+      <c r="E48" s="3">
         <v>287400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>302400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>300300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>320400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>320900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>314600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>360500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>354600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>352700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>401800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>388300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>442600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>455900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>401600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>383700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>375200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>409300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>657700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>459300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>470800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>423800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>435500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>442000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>484200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>474700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>518600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>537200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>544000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>520800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>322100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>297600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>295100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>297800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>356500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>333500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>360300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>366700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>388600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>353000</v>
       </c>
-      <c r="AQ48" s="3">
+      <c r="AR48" s="3">
         <v>351900</v>
       </c>
     </row>
-    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E49" s="3">
         <v>89400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>101600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>80600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>84600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>84900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>89200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>99600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>95900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>92000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>111300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>106700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>117500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>129000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>116400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>106700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>98900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>104500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>111600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>107800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>105800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>92100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>92400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>85700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>88100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>83700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>93200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>86800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>87500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>82300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>85000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>74100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>78200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>79900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>92900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>86900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>87200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>86900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>87700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>85800</v>
       </c>
-      <c r="AQ49" s="3">
+      <c r="AR49" s="3">
         <v>83900</v>
       </c>
     </row>
-    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5555,8 +5669,11 @@
       <c r="AQ50" s="3">
         <v>0</v>
       </c>
+      <c r="AR50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5680,133 +5797,139 @@
       <c r="AQ51" s="3">
         <v>0</v>
       </c>
+      <c r="AR51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E52" s="3">
         <v>141600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>231300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>195800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>242600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>230400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>178100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>336900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>183400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>235200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>199400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>280200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>352300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>390800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>373200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>358700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>369800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>384600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>516500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>982400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>824600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>677600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>628100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>639300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>668800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>585900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>588700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>586900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>541300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>543100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>487400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>482600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>488300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>478300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>568200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>563500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>534600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>543900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>565200</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>529700</v>
       </c>
-      <c r="AQ52" s="3">
+      <c r="AR52" s="3">
         <v>512800</v>
       </c>
     </row>
-    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5930,133 +6053,139 @@
       <c r="AQ53" s="3">
         <v>0</v>
       </c>
+      <c r="AR53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>76330500</v>
+      </c>
+      <c r="E54" s="3">
         <v>75174900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>75654500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>70964500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71065700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>70456900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>68835600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>73423500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>72412000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>76325100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>80822500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>81171200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>85572200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>87743200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>73617800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>81791500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>75137500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>69456900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>74453000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>80265600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>74104100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>61024900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>62469200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>66315500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>75673200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>70579400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>64234400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>63348000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>58004100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>51567800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>49780600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>47151800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>48114200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>46635300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>52632300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>51674500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>51165500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>53961600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>55880000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>54058400</v>
       </c>
-      <c r="AQ54" s="3">
+      <c r="AR54" s="3">
         <v>54546900</v>
       </c>
     </row>
-    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -6100,8 +6229,9 @@
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
       <c r="AQ55" s="3"/>
+      <c r="AR55" s="3"/>
     </row>
-    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6145,217 +6275,221 @@
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
       <c r="AQ56" s="3"/>
+      <c r="AR56" s="3"/>
     </row>
-    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>33860000</v>
+      </c>
+      <c r="E57" s="3">
         <v>32195400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>34435700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31075200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31051800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>31393200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>31882500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32060200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30028200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>30072900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>32301600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>30774300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>33788800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34136100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1245000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1262200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>881900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1142300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>805100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>456300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1200100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>315100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>405000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>505100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>353200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>746800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>251800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>338000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>541600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>358400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>207100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>564700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>918000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>453200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>715500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>755200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>379900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>885400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>435600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>874700</v>
       </c>
-      <c r="AQ57" s="3">
+      <c r="AR57" s="3">
         <v>800000</v>
       </c>
     </row>
-    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19769000</v>
+      </c>
+      <c r="E58" s="3">
         <v>20629800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>21564100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20785400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>20411700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>19596200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19553700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20856200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>23036400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>27300500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>27488200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>28542600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>29323100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>23690300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4759700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5122600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6496800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>10947300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5774200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6317100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4498200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5705900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4340600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5959500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7620400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7175200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>6433000</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
       <c r="AE58" s="3">
         <v>0</v>
       </c>
@@ -6395,178 +6529,184 @@
       <c r="AQ58" s="3">
         <v>0</v>
       </c>
+      <c r="AR58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4849800</v>
+      </c>
+      <c r="E59" s="3">
         <v>4722500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1581000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2757600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2602200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3160100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>806900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4789900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4195700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4288400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3503600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5674800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4742600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5394500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>428500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>324500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>212600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>394900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>318300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>26300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>23000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>30400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>78400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>77200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>12800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>12200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>17600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>39300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>47200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>16800</v>
       </c>
-      <c r="AQ59" s="3">
+      <c r="AR59" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>58558200</v>
+      </c>
+      <c r="E60" s="3">
         <v>57617400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>57672600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>54710100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>54147100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>54217600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>52324200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>57742700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>57285400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>61714400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>63344600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>65035100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>67892300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>63287900</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6645,258 +6785,267 @@
       <c r="AQ60" s="3">
         <v>0</v>
       </c>
+      <c r="AR60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10028800</v>
+      </c>
+      <c r="E61" s="3">
         <v>9429800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8887000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9097200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9713100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9288000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8477700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10176700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9801500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9623800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10419900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10536500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11516800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18480100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>15868600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>15590500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>14499900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8706100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>15852700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>16137100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>16523100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>11629300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>13651100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>12284400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>11716400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9716700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>10076600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>15840400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>15362800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>13831700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>13784300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>13556700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>13376400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>13022000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>13280000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>12535000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>13408200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>13438200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>14319000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>12892300</v>
       </c>
-      <c r="AQ61" s="3">
+      <c r="AR61" s="3">
         <v>12894600</v>
       </c>
     </row>
-    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2152800</v>
+      </c>
+      <c r="E62" s="3">
         <v>2855800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2717500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2251300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2227700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2212200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2637100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>683300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>764900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>602500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1927300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>666400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>723700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>874700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>544700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>540900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>483100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>482500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1470000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1112400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>835700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>759700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>655400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>514700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>460200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>544100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>555000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>498100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>346800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>522700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>438600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>382900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>293100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>449400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>491000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>417400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>363200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>494200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>478200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>419600</v>
       </c>
-      <c r="AQ62" s="3">
+      <c r="AR62" s="3">
         <v>354800</v>
       </c>
     </row>
-    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -7020,8 +7169,11 @@
       <c r="AQ63" s="3">
         <v>0</v>
       </c>
+      <c r="AR63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -7145,8 +7297,11 @@
       <c r="AQ64" s="3">
         <v>0</v>
       </c>
+      <c r="AR64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7270,133 +7425,139 @@
       <c r="AQ65" s="3">
         <v>0</v>
       </c>
+      <c r="AR65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>70753300</v>
+      </c>
+      <c r="E66" s="3">
         <v>69911600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>69286300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>66069100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>66098800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>65721100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>63442700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>68605000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67854300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>71945900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>75698900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>76336700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>80229900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>82650400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>69158700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>77581400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>71333800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>65269800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>70200200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>76131600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>69908200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>57032600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>58473100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>62085000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>71192000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>66421100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>59928000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>58780600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>53471000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>47249500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>45666400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>43325500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>44274400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>42577900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>48125000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>47305700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>46909400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>49597900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>51548300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>49839300</v>
       </c>
-      <c r="AQ66" s="3">
+      <c r="AR66" s="3">
         <v>50462800</v>
       </c>
     </row>
-    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7440,8 +7601,9 @@
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
       <c r="AQ67" s="3"/>
+      <c r="AR67" s="3"/>
     </row>
-    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7565,8 +7727,11 @@
       <c r="AQ68" s="3">
         <v>0</v>
       </c>
+      <c r="AR68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7690,8 +7855,11 @@
       <c r="AQ69" s="3">
         <v>0</v>
       </c>
+      <c r="AR69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7815,8 +7983,11 @@
       <c r="AQ70" s="3">
         <v>0</v>
       </c>
+      <c r="AR70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7940,133 +8111,139 @@
       <c r="AQ71" s="3">
         <v>0</v>
       </c>
+      <c r="AR71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>321300</v>
+      </c>
+      <c r="E72" s="3">
         <v>582300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>734500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>358600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>272500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>398700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>502300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>224600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>179700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>247900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>417300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>279900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>271600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>548400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3677000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3642500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3410800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3683800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3624600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3690800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3535600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3171200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3028700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3180000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3308100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3104000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3184700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3351800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3267100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3152700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2968400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2762400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2735200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2922100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3200500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3061900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2920600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3043500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2975900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2861000</v>
       </c>
-      <c r="AQ72" s="3">
+      <c r="AR72" s="3">
         <v>2732100</v>
       </c>
     </row>
-    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8190,8 +8367,11 @@
       <c r="AQ73" s="3">
         <v>0</v>
       </c>
+      <c r="AR73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8315,8 +8495,11 @@
       <c r="AQ74" s="3">
         <v>0</v>
       </c>
+      <c r="AR74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8440,133 +8623,139 @@
       <c r="AQ75" s="3">
         <v>0</v>
       </c>
+      <c r="AR75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5399100</v>
+      </c>
+      <c r="E76" s="3">
         <v>5097200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6235100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4775700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4847000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4623200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5287800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4701200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4449400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4249000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4981300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4694700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5193600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4949400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4459100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4210100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3803700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4187100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4252900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4134100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4195800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3992300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3996100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4230400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4481100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4158400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4306300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4567400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4533100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4318300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4114200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3826400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3839800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4057400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4507300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4368700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4256000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4363700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4331700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4219100</v>
       </c>
-      <c r="AQ76" s="3">
+      <c r="AR76" s="3">
         <v>4084100</v>
       </c>
     </row>
-    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8690,263 +8879,272 @@
       <c r="AQ77" s="3">
         <v>0</v>
       </c>
+      <c r="AR77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AQ80" s="2">
+      <c r="AR80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>415300</v>
+      </c>
+      <c r="E81" s="3">
         <v>293800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>248400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>257400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>292600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>291900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>273600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>270900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>231000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>122700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>201800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>63400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>158500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>171300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>109900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>202300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>302600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>266400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>271900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>222400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>236900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>203900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>205400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>122000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>105200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>171400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>148200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>188700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>236300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>163100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>198900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>160900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>197800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>193300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>198000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>201900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>221100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>209300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>164000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>184200</v>
       </c>
-      <c r="AQ81" s="3">
+      <c r="AR81" s="3">
         <v>175600</v>
       </c>
     </row>
-    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8990,133 +9188,137 @@
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
       <c r="AQ82" s="3"/>
+      <c r="AR82" s="3"/>
     </row>
-    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E83" s="3">
         <v>23800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>22700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>22300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>25800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>27300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>28700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>22400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>27900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>36500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>35000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>34400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>35700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>37000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>40500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>38500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>31100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>30800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>30900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>34200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>33000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>35100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>36400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>35200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>34000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>27400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>23900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>24700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>24600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>32900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>28000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>27600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>25900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>28400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>24700</v>
       </c>
-      <c r="AQ83" s="3">
+      <c r="AR83" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9240,8 +9442,11 @@
       <c r="AQ84" s="3">
         <v>0</v>
       </c>
+      <c r="AR84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9365,8 +9570,11 @@
       <c r="AQ85" s="3">
         <v>0</v>
       </c>
+      <c r="AR85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9490,8 +9698,11 @@
       <c r="AQ86" s="3">
         <v>0</v>
       </c>
+      <c r="AR86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9615,8 +9826,11 @@
       <c r="AQ87" s="3">
         <v>0</v>
       </c>
+      <c r="AR87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9740,133 +9954,139 @@
       <c r="AQ88" s="3">
         <v>0</v>
       </c>
+      <c r="AR88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-123000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-628200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-408700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>565700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>963900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-198700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1204800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>477400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>537900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1123000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>144100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1299500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1107200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-306100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>319500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-847900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-219500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1236600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4011300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2810400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5591400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>698200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-72100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-493800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-405400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1781900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>319600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1033900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-736200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>254900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>592900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>244800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>195000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>368200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-45200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-307900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-604900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1362500</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-1128900</v>
       </c>
-      <c r="AQ89" s="3">
+      <c r="AR89" s="3">
         <v>1853300</v>
       </c>
     </row>
-    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9910,133 +10130,137 @@
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
       <c r="AQ90" s="3"/>
+      <c r="AR90" s="3"/>
     </row>
-    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-51100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-8900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-34000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-26600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-51843000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-23549000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15583000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7455000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-20501000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18990000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-14000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-14300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-32200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-13300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-39100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-14100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-47900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-17100</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-14800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-6500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-66200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AQ91" s="3">
+      <c r="AR91" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -10160,8 +10384,11 @@
       <c r="AQ92" s="3">
         <v>0</v>
       </c>
+      <c r="AR92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10285,133 +10512,139 @@
       <c r="AQ93" s="3">
         <v>0</v>
       </c>
+      <c r="AR93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-53400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-15100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-20700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-24200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-54300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-15300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-44300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-39300</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-16400</v>
       </c>
       <c r="P94" s="3">
         <v>-16400</v>
       </c>
       <c r="Q94" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="R94" s="3">
         <v>-53900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-24000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-32100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-26800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-30300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-15600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-20900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-129300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-21700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-82600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>52300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-49600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-34800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-20400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-10900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-61800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-9600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-21100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-15400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-66200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-27700</v>
       </c>
-      <c r="AQ94" s="3">
+      <c r="AR94" s="3">
         <v>-29200</v>
       </c>
     </row>
-    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10455,62 +10688,63 @@
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
       <c r="AQ95" s="3"/>
+      <c r="AR95" s="3"/>
     </row>
-    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3">
+        <v>685900</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>644600</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>368600</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>604500</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-492900</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -10518,17 +10752,17 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-391200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-185500</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -10542,11 +10776,11 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-490100</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -10554,11 +10788,11 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-542200</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
@@ -10580,8 +10814,11 @@
       <c r="AQ96" s="3">
         <v>0</v>
       </c>
+      <c r="AR96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10705,8 +10942,11 @@
       <c r="AQ97" s="3">
         <v>0</v>
       </c>
+      <c r="AR97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10830,8 +11070,11 @@
       <c r="AQ98" s="3">
         <v>0</v>
       </c>
+      <c r="AR98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10955,379 +11198,391 @@
       <c r="AQ99" s="3">
         <v>0</v>
       </c>
+      <c r="AR99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>156100</v>
+      </c>
+      <c r="E100" s="3">
         <v>640400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-343400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1262700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-414800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2042000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-583000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1214400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1133300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>134000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1459000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>736900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1181700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-682900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>258600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-311600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-520400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1761700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-544200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>243000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>253300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-221800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-14800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>188000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>191900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>5400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-484200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>168300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-703600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-10300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-11900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-474100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-12000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-18400</v>
       </c>
-      <c r="AP100" s="3">
-        <v>0</v>
-      </c>
       <c r="AQ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR100" s="3">
         <v>-506400</v>
       </c>
     </row>
-    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="E101" s="3">
         <v>4900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>7800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-13600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>19900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8300</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>10300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>21600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>30100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-27200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>19900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>31500</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-24200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>157700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>365700</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>14100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-153600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-108200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-18700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>258000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>76200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>97700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>48600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-52500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>92700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-46100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>122300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-21600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-5700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-48000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>50200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-42700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-37400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>33700</v>
       </c>
-      <c r="AQ101" s="3">
+      <c r="AR101" s="3">
         <v>-77100</v>
       </c>
     </row>
-    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E102" s="3">
         <v>18700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>27300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>212200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-326700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-632800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>790700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-134600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-705400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>10500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>225500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>120300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-376400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>855700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-397400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-581800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-546300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>683700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3194700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2491900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5168400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>676000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-477900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-632400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>151700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>39100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1734200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>389900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>515700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-741800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>466300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>509100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-356900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>157300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>290300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-114700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-752900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-675000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1240600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-1122800</v>
       </c>
-      <c r="AQ102" s="3">
+      <c r="AR102" s="3">
         <v>1240600</v>
       </c>
     </row>
